--- a/data/vendor-search/results_all_ev-charging.xlsx
+++ b/data/vendor-search/results_all_ev-charging.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:H19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -450,6 +450,11 @@
       <c r="G1" t="inlineStr">
         <is>
           <t>cpe_strings</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>matched_terms</t>
         </is>
       </c>
     </row>
@@ -493,6 +498,11 @@
         </is>
       </c>
       <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>juicebox</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -529,6 +539,11 @@
           <t>cpe:2.3:o:chargepoint:home_flex_firmware:5.5.3.13:*:*:*:*:*:*:*|cpe:2.3:h:chargepoint:home_flex:-:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>chargepoint home|chargepoint home flex</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -565,6 +580,11 @@
           <t>cpe:2.3:o:chargepoint:home_flex_firmware:5.5.3.13:*:*:*:*:*:*:*|cpe:2.3:h:chargepoint:home_flex:-:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>chargepoint home|chargepoint home flex</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -601,6 +621,11 @@
           <t>cpe:2.3:o:chargepoint:home_flex_nema_14-50_plug_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:chargepoint:home_flex_nema_14-50_plug:-:*:*:*:*:*:*:*|cpe:2.3:o:chargepoint:home_flex_hardwired_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:chargepoint:home_flex_hardwired:-:*:*:*:*:*:*:*|cpe:2.3:o:chargepoint:home_flex_nema_6-50_plug_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:chargepoint:home_flex_nema_6-50_plug:-:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>chargepoint home|chargepoint home flex</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -637,6 +662,11 @@
           <t>cpe:2.3:o:chargepoint:home_flex_nema_14-50_plug_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:chargepoint:home_flex_nema_14-50_plug:-:*:*:*:*:*:*:*|cpe:2.3:o:chargepoint:home_flex_hardwired_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:chargepoint:home_flex_hardwired:-:*:*:*:*:*:*:*|cpe:2.3:o:chargepoint:home_flex_nema_6-50_plug_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:chargepoint:home_flex_nema_6-50_plug:-:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>chargepoint home|chargepoint home flex</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -673,6 +703,11 @@
           <t>cpe:2.3:o:chargepoint:home_flex_nema_14-50_plug_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:chargepoint:home_flex_nema_14-50_plug:-:*:*:*:*:*:*:*|cpe:2.3:o:chargepoint:home_flex_hardwired_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:chargepoint:home_flex_hardwired:-:*:*:*:*:*:*:*|cpe:2.3:o:chargepoint:home_flex_nema_6-50_plug_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:chargepoint:home_flex_nema_6-50_plug:-:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>chargepoint home|chargepoint home flex</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -709,6 +744,11 @@
           <t>cpe:2.3:o:chargepoint:home_flex_nema_14-50_plug_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:chargepoint:home_flex_nema_14-50_plug:-:*:*:*:*:*:*:*|cpe:2.3:o:chargepoint:home_flex_hardwired_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:chargepoint:home_flex_hardwired:-:*:*:*:*:*:*:*|cpe:2.3:o:chargepoint:home_flex_nema_6-50_plug_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:chargepoint:home_flex_nema_6-50_plug:-:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>chargepoint home|chargepoint home flex</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -745,6 +785,11 @@
           <t>cpe:2.3:o:chargepoint:home_flex_nema_14-50_plug_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:chargepoint:home_flex_nema_14-50_plug:-:*:*:*:*:*:*:*|cpe:2.3:o:chargepoint:home_flex_hardwired_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:chargepoint:home_flex_hardwired:-:*:*:*:*:*:*:*|cpe:2.3:o:chargepoint:home_flex_nema_6-50_plug_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:chargepoint:home_flex_nema_6-50_plug:-:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>chargepoint home|chargepoint home flex</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -781,6 +826,11 @@
           <t>cpe:2.3:o:chargepoint:home_flex_nema_14-50_plug_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:chargepoint:home_flex_nema_14-50_plug:-:*:*:*:*:*:*:*|cpe:2.3:o:chargepoint:home_flex_hardwired_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:chargepoint:home_flex_hardwired:-:*:*:*:*:*:*:*|cpe:2.3:o:chargepoint:home_flex_nema_6-50_plug_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:chargepoint:home_flex_nema_6-50_plug:-:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>chargepoint home|chargepoint home flex</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -812,6 +862,11 @@
         </is>
       </c>
       <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>versicharge</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -843,6 +898,11 @@
         </is>
       </c>
       <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>versicharge</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -879,6 +939,11 @@
           <t>cpe:2.3:o:tesla:wall_connector_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:tesla:wall_connector:-:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>tesla wall connector</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -915,6 +980,11 @@
           <t>cpe:2.3:o:tesla:wall_connector_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:tesla:wall_connector:-:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>tesla wall connector</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -946,6 +1016,11 @@
         </is>
       </c>
       <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>chargepoint home|chargepoint home flex</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -978,6 +1053,11 @@
         </is>
       </c>
       <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>juicebox|enel x juicebox</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1014,6 +1094,11 @@
           <t>cpe:2.3:o:chargepoint:home_flex_cph50_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:chargepoint:home_flex_cph50:-:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>chargepoint home|chargepoint home flex</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1050,6 +1135,11 @@
           <t>cpe:2.3:o:chargepoint:home_flex_cph50_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:chargepoint:home_flex_cph50:-:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>chargepoint home|chargepoint home flex</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1084,6 +1174,11 @@
       <c r="G19" t="inlineStr">
         <is>
           <t>cpe:2.3:o:chargepoint:home_flex_cph50_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:chargepoint:home_flex_cph50:-:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>chargepoint home|chargepoint home flex</t>
         </is>
       </c>
     </row>
